--- a/site/EntraID-ABC-Fitness/headings.xlsx
+++ b/site/EntraID-ABC-Fitness/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Data Protection Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -787,6 +787,270 @@
       <c r="D17" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFKVWW6D31B41CPSSE0MK3S</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KKXKNHW297KGFRCENNAR6GMR</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KKXKNHW297KGFRCENNAR6GMR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KMFNN6EW7R1SAYGSYWR04NF5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFNN6EW7R1SAYGSYWR04NF5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMHWW75VTB7V8GZ6H6YC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMHWW75VTB7V8GZ6H6YC</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notification Template Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMHX61RD9PQ35ZE43A5W</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMHX61RD9PQ35ZE43A5W</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Success Notifications</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMHYZSAAGVSXR93ZY8N4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMHYZSAAGVSXR93ZY8N4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Failure Notifications</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMJ0Y41CR7GXATDDAPPY</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMJ0Y41CR7GXATDDAPPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Skipped Notifications</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMJ1SG9JWBDBDWQ9JF0M</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMJ1SG9JWBDBDWQ9JF0M</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KMFQBMJ26WASNG3WN8P510G8</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFQBMJ26WASNG3WN8P510G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KJBZZH5XZG9CGR1VQ8SGBP6R</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KMFRJ0QPS1JED0CWF4YXJWPN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFRJ0QPS1JED0CWF4YXJWPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Debug Settings</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KMFRJ0QSWMTN06X2MEGKX4FA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFRJ0QSWMTN06X2MEGKX4FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Source Filter</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KMFRJ0QT3XPYW1TWQ61J7CAC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFRJ0QT3XPYW1TWQ61J7CAC</t>
         </is>
       </c>
     </row>

--- a/site/EntraID-ABC-Fitness/headings.xlsx
+++ b/site/EntraID-ABC-Fitness/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,204 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KMFX5J0QQE4B4HRWF0S7YNVT</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFX5J0QQE4B4HRWF0S7YNVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Employee Mapper</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KMFXHYATW0N5ASN6BHSTTKZ8</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFXHYATW0N5ASN6BHSTTKZ8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KMFXJ482YABB0HF3K3BX0XQY</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFXJ482YABB0HF3K3BX0XQY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Available Tables</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KMFXJ4826F1X662B8EM96JZD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFXJ4826F1X662B8EM96JZD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Managing Table Data</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KMFXJ483EEDRCGB6PGTK2VR4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KMFXJ483EEDRCGB6PGTK2VR4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/EntraID-ABC-Fitness/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
